--- a/bills/JXZFSP01/-5203055703/e9728d3dadbdcb43d98de0ee76340cbfb74b529f033dbb9a5ed6980eac35d23c/bill-all.xlsx
+++ b/bills/JXZFSP01/-5203055703/e9728d3dadbdcb43d98de0ee76340cbfb74b529f033dbb9a5ed6980eac35d23c/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/18 12:52:59</t>
+          <t>08/24 13:50:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/13 17:37:32</t>
+          <t>08/18 12:52:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>30487</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20 17:45:55</t>
+          <t>08/13 17:37:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20 16:19:16</t>
+          <t>07/20 17:45:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,12 +478,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/19 20:42:01</t>
+          <t>07/20 16:19:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>252</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -505,83 +505,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/19 20:42:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/19 20:41:31</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>14976</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>755000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90234.2</t>
+          <t>755000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>81953</t>
+          <t>90234.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>82341</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>8281.2</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7893.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5203055703/e9728d3dadbdcb43d98de0ee76340cbfb74b529f033dbb9a5ed6980eac35d23c/bill-all.xlsx
+++ b/bills/JXZFSP01/-5203055703/e9728d3dadbdcb43d98de0ee76340cbfb74b529f033dbb9a5ed6980eac35d23c/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/24 13:50:19</t>
+          <t>08/24 14:08:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>22867</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/18 12:52:59</t>
+          <t>08/24 13:50:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/13 17:37:32</t>
+          <t>08/18 12:52:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>30487</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20 17:45:55</t>
+          <t>08/13 17:37:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,12 +478,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/20 16:19:16</t>
+          <t>07/20 17:45:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -505,12 +505,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/19 20:42:01</t>
+          <t>07/20 16:19:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>252</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -532,83 +532,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/19 20:42:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/19 20:41:31</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>14976</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>755000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90234.2</t>
+          <t>755000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>82341</t>
+          <t>90234.2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>105208</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7893.2</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-14973.8</t>
         </is>
       </c>
     </row>
